--- a/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="683">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:47:58+00:00</t>
+    <t>2023-11-28T12:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3506,10 +3509,10 @@
         <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3559,7 +3562,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3594,10 +3597,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3620,16 +3623,16 @@
         <v>93</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3679,7 +3682,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3714,10 +3717,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3740,16 +3743,16 @@
         <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3775,13 +3778,13 @@
         <v>81</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>81</v>
@@ -3799,7 +3802,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3820,10 +3823,10 @@
         <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>81</v>
@@ -3834,10 +3837,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3860,16 +3863,16 @@
         <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3895,13 +3898,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3919,7 +3922,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3940,10 +3943,10 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
@@ -3954,10 +3957,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3983,13 +3986,13 @@
         <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4039,7 +4042,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4074,10 +4077,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4100,16 +4103,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4135,13 +4138,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4159,7 +4162,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4194,14 +4197,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4220,16 +4223,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4279,7 +4282,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4303,7 +4306,7 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -4314,14 +4317,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4340,16 +4343,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4399,7 +4402,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4434,10 +4437,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4466,7 +4469,7 @@
         <v>116</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>118</v>
@@ -4519,7 +4522,7 @@
         <v>121</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4554,13 +4557,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>114</v>
@@ -4582,13 +4585,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>118</v>
@@ -4641,7 +4644,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4676,13 +4679,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4704,13 +4707,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4761,7 +4764,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4796,10 +4799,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4825,16 +4828,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4883,7 +4886,7 @@
         <v>121</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4918,10 +4921,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4944,17 +4947,17 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -5003,7 +5006,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -5018,19 +5021,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5038,14 +5041,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5064,19 +5067,19 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -5125,7 +5128,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5137,19 +5140,19 @@
         <v>104</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5160,14 +5163,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5186,16 +5189,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5245,7 +5248,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5257,19 +5260,19 @@
         <v>104</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -5280,10 +5283,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5306,19 +5309,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5343,13 +5346,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5367,7 +5370,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>92</v>
@@ -5382,19 +5385,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5402,10 +5405,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5428,19 +5431,19 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5465,19 +5468,19 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5487,7 +5490,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5508,13 +5511,13 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5522,13 +5525,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>81</v>
@@ -5550,19 +5553,19 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5587,13 +5590,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5611,7 +5614,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5632,13 +5635,13 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5646,10 +5649,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5764,10 +5767,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5884,10 +5887,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5910,19 +5913,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5971,7 +5974,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5992,10 +5995,10 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -6006,10 +6009,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6124,10 +6127,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6244,10 +6247,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6273,23 +6276,23 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -6331,7 +6334,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6352,10 +6355,10 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -6366,10 +6369,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6395,13 +6398,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6451,7 +6454,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6472,10 +6475,10 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6486,10 +6489,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6512,26 +6515,26 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -6573,7 +6576,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6594,10 +6597,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6608,10 +6611,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6637,16 +6640,16 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6695,7 +6698,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6716,10 +6719,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6730,10 +6733,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6756,19 +6759,19 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6817,7 +6820,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6838,10 +6841,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6852,10 +6855,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6881,16 +6884,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6939,7 +6942,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6960,10 +6963,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6974,14 +6977,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7000,19 +7003,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -7037,13 +7040,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -7061,7 +7064,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>92</v>
@@ -7076,30 +7079,30 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7214,10 +7217,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7334,10 +7337,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7360,19 +7363,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7409,7 +7412,7 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7419,7 +7422,7 @@
         <v>121</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7440,10 +7443,10 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7454,13 +7457,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -7482,19 +7485,19 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7543,7 +7546,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7564,10 +7567,10 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7578,10 +7581,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7696,10 +7699,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7816,10 +7819,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7845,23 +7848,23 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>81</v>
@@ -7903,7 +7906,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7924,10 +7927,10 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7938,10 +7941,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7967,13 +7970,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8023,7 +8026,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8044,10 +8047,10 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -8058,10 +8061,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8084,26 +8087,26 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -8145,7 +8148,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8166,10 +8169,10 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -8180,10 +8183,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8209,16 +8212,16 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8267,7 +8270,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8288,10 +8291,10 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -8302,10 +8305,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8328,19 +8331,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8389,7 +8392,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8410,10 +8413,10 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8424,10 +8427,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8453,16 +8456,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8511,7 +8514,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8532,10 +8535,10 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8546,10 +8549,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8572,19 +8575,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8633,7 +8636,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8645,22 +8648,22 @@
         <v>104</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
@@ -8668,10 +8671,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8694,16 +8697,16 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8753,7 +8756,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8765,7 +8768,7 @@
         <v>104</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8774,13 +8777,13 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -8788,14 +8791,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8814,19 +8817,19 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8875,7 +8878,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8887,22 +8890,22 @@
         <v>104</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -8910,14 +8913,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8936,19 +8939,19 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8997,7 +9000,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9006,25 +9009,25 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9032,10 +9035,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9061,13 +9064,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9117,7 +9120,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9138,13 +9141,13 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>81</v>
@@ -9152,10 +9155,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9178,19 +9181,19 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -9239,7 +9242,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9251,22 +9254,22 @@
         <v>104</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>81</v>
@@ -9274,10 +9277,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9300,19 +9303,19 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9349,17 +9352,17 @@
         <v>81</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9368,7 +9371,7 @@
         <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -9377,30 +9380,30 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>81</v>
@@ -9422,19 +9425,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9444,7 +9447,7 @@
         <v>81</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>81</v>
@@ -9483,7 +9486,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9492,7 +9495,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9501,27 +9504,27 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9636,10 +9639,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9756,10 +9759,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9782,19 +9785,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9843,7 +9846,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9864,10 +9867,10 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9878,10 +9881,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9904,25 +9907,25 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R62" t="s" s="2">
         <v>81</v>
@@ -9943,13 +9946,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9967,7 +9970,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9988,10 +9991,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -10002,10 +10005,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10031,16 +10034,16 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -10089,7 +10092,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10110,10 +10113,10 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -10124,10 +10127,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10153,23 +10156,23 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>81</v>
@@ -10211,7 +10214,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10220,7 +10223,7 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10232,10 +10235,10 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -10246,10 +10249,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10272,19 +10275,19 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10309,13 +10312,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -10333,7 +10336,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10354,10 +10357,10 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -10368,10 +10371,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10394,19 +10397,19 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10431,13 +10434,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -10455,7 +10458,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10464,7 +10467,7 @@
         <v>92</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10479,7 +10482,7 @@
         <v>106</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -10490,10 +10493,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10608,10 +10611,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10728,10 +10731,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10754,19 +10757,19 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10815,7 +10818,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10836,10 +10839,10 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
@@ -10850,10 +10853,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10968,10 +10971,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11088,10 +11091,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11117,16 +11120,16 @@
         <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11175,7 +11178,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11196,10 +11199,10 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
@@ -11210,10 +11213,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11239,13 +11242,13 @@
         <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11295,7 +11298,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11316,10 +11319,10 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>81</v>
@@ -11330,10 +11333,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11356,19 +11359,19 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11417,7 +11420,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11438,10 +11441,10 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11452,10 +11455,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11481,16 +11484,16 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11539,7 +11542,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11560,10 +11563,10 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11574,10 +11577,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11600,19 +11603,19 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11661,7 +11664,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11682,10 +11685,10 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11696,10 +11699,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11725,16 +11728,16 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11783,7 +11786,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11804,10 +11807,10 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11818,14 +11821,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11844,19 +11847,19 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11881,11 +11884,11 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11903,7 +11906,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11921,27 +11924,27 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11964,19 +11967,19 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -12025,7 +12028,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12046,10 +12049,10 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -12060,10 +12063,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12086,16 +12089,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12121,13 +12124,13 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -12145,7 +12148,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12163,27 +12166,27 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12197,7 +12200,7 @@
         <v>92</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>81</v>
@@ -12206,19 +12209,19 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -12243,13 +12246,11 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -12267,7 +12268,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12288,10 +12289,10 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12302,10 +12303,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12328,16 +12329,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12387,7 +12388,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12399,33 +12400,33 @@
         <v>104</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12448,16 +12449,16 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12507,7 +12508,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12519,33 +12520,33 @@
         <v>104</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12568,19 +12569,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12629,7 +12630,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12641,7 +12642,7 @@
         <v>104</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -12650,10 +12651,10 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12664,10 +12665,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12782,10 +12783,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12902,14 +12903,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12931,16 +12932,16 @@
         <v>115</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12989,7 +12990,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13024,10 +13025,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13050,16 +13051,16 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13109,7 +13110,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13118,10 +13119,10 @@
         <v>92</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
@@ -13130,10 +13131,10 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -13144,10 +13145,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13170,16 +13171,16 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13229,7 +13230,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13238,10 +13239,10 @@
         <v>92</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
@@ -13250,10 +13251,10 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -13264,10 +13265,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13290,19 +13291,19 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13327,13 +13328,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13351,7 +13352,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13369,13 +13370,13 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13386,10 +13387,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13412,19 +13413,19 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13449,13 +13450,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -13473,7 +13474,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13491,13 +13492,13 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13508,10 +13509,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13534,19 +13535,19 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -13595,7 +13596,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13607,7 +13608,7 @@
         <v>104</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -13616,10 +13617,10 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13630,10 +13631,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13659,13 +13660,13 @@
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13715,7 +13716,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13736,10 +13737,10 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13750,10 +13751,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13776,16 +13777,16 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13835,7 +13836,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13847,7 +13848,7 @@
         <v>104</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13856,10 +13857,10 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13870,10 +13871,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13896,16 +13897,16 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13955,7 +13956,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13967,7 +13968,7 @@
         <v>104</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>81</v>
@@ -13976,10 +13977,10 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13990,10 +13991,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14016,19 +14017,19 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14077,7 +14078,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14089,7 +14090,7 @@
         <v>104</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
@@ -14098,10 +14099,10 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14112,10 +14113,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14230,10 +14231,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14350,14 +14351,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14379,16 +14380,16 @@
         <v>115</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14437,7 +14438,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14472,10 +14473,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14498,19 +14499,19 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14535,13 +14536,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14559,7 +14560,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>92</v>
@@ -14577,16 +14578,16 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -14594,10 +14595,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14620,19 +14621,19 @@
         <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14657,13 +14658,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -14681,7 +14682,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14690,7 +14691,7 @@
         <v>92</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>105</v>
@@ -14699,27 +14700,27 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14742,19 +14743,19 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14779,13 +14780,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14803,7 +14804,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14812,7 +14813,7 @@
         <v>92</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14827,7 +14828,7 @@
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14838,14 +14839,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14864,19 +14865,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14901,31 +14902,31 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14943,27 +14944,27 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14989,16 +14990,16 @@
         <v>82</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15047,7 +15048,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15068,10 +15069,10 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
